--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123350284</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>58159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R3" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +902,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351625</v>
+        <v>123351085</v>
       </c>
       <c r="B4" t="n">
-        <v>58156</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -980,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500620</v>
+        <v>500362</v>
       </c>
       <c r="R4" t="n">
-        <v>6576968</v>
+        <v>6576865</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,6 +1029,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351625</v>
+        <v>123351085</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500620</v>
+        <v>500362</v>
       </c>
       <c r="R3" t="n">
-        <v>6576968</v>
+        <v>6576865</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +907,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>58159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +956,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,7 +980,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R4" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,26 +1049,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123350284</v>
+        <v>123351625</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>58159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500607</v>
+        <v>500620</v>
       </c>
       <c r="R2" t="n">
-        <v>6577056</v>
+        <v>6576968</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351625</v>
+        <v>123350284</v>
       </c>
       <c r="B4" t="n">
-        <v>58159</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500620</v>
+        <v>500607</v>
       </c>
       <c r="R4" t="n">
-        <v>6576968</v>
+        <v>6577056</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123350284</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351625</v>
+        <v>123351085</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500620</v>
+        <v>500362</v>
       </c>
       <c r="R3" t="n">
-        <v>6576968</v>
+        <v>6576865</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +907,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>58165</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +956,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,7 +980,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R4" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,26 +1049,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123350284</v>
+        <v>123351625</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>58168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500607</v>
+        <v>500620</v>
       </c>
       <c r="R2" t="n">
-        <v>6577056</v>
+        <v>6576968</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
         <v>123351085</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351625</v>
+        <v>123350284</v>
       </c>
       <c r="B4" t="n">
-        <v>58165</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500620</v>
+        <v>500607</v>
       </c>
       <c r="R4" t="n">
-        <v>6576968</v>
+        <v>6577056</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123351625</v>
+        <v>123351085</v>
       </c>
       <c r="B2" t="n">
-        <v>58168</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500620</v>
+        <v>500362</v>
       </c>
       <c r="R2" t="n">
-        <v>6576968</v>
+        <v>6576865</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +785,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +834,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +858,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R3" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,26 +927,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,7 +947,7 @@
         <v>123350284</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R2" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351625</v>
+        <v>123350284</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -867,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500620</v>
+        <v>500607</v>
       </c>
       <c r="R3" t="n">
-        <v>6576968</v>
+        <v>6577056</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123350284</v>
+        <v>123351085</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -980,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500607</v>
+        <v>500362</v>
       </c>
       <c r="R4" t="n">
-        <v>6577056</v>
+        <v>6576865</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,6 +1029,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123351625</v>
+        <v>123350284</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500620</v>
+        <v>500607</v>
       </c>
       <c r="R2" t="n">
-        <v>6576968</v>
+        <v>6577056</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123350284</v>
+        <v>123351625</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500607</v>
+        <v>500620</v>
       </c>
       <c r="R3" t="n">
-        <v>6577056</v>
+        <v>6576968</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123350284</v>
+        <v>123351625</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500607</v>
+        <v>500620</v>
       </c>
       <c r="R2" t="n">
-        <v>6577056</v>
+        <v>6576968</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123351625</v>
+        <v>123350284</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500620</v>
+        <v>500607</v>
       </c>
       <c r="R3" t="n">
-        <v>6576968</v>
+        <v>6577056</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 13627-2025 artfynd.xlsx
+++ b/artfynd/A 13627-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123351625</v>
+        <v>123351085</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500620</v>
+        <v>500362</v>
       </c>
       <c r="R2" t="n">
-        <v>6576968</v>
+        <v>6576865</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +785,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -919,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123351085</v>
+        <v>123351625</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +956,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,7 +980,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +989,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500362</v>
+        <v>500620</v>
       </c>
       <c r="R4" t="n">
-        <v>6576865</v>
+        <v>6576968</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i granlåga</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,26 +1049,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
